--- a/Data Files/Backoffce/IndexacaoFG/Arquivos/Relatório de Recusas  28.07.2025 a 03.08.2025.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/Arquivos/Relatório de Recusas  28.07.2025 a 03.08.2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29122"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29128"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms.sharepoint.com/teams/BR0010-4356589/Shared Documents/BACK-OFFICE SME/Santander/2025/Relatório de Recusas/05. Maio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9AF77D62-0DE4-42A1-BBD8-4335290150DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E7B21216-FB5A-46BA-9299-A988CD759C92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="28.07" sheetId="8" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="151">
   <si>
     <t>SEGURADORA</t>
   </si>
@@ -427,6 +427,99 @@
   </si>
   <si>
     <t xml:space="preserve">ORLANDO KAKIMOTO                             </t>
+  </si>
+  <si>
+    <t>SANDRA ALVES DA SILVEIRA CPF 07169148919</t>
+  </si>
+  <si>
+    <t>Risco coberto pela apólice 5177202425311879766, outro corretor</t>
+  </si>
+  <si>
+    <t>RUDOLF FUHRMANN FILHO CPF 001.797.422-48</t>
+  </si>
+  <si>
+    <t>Duplicidade;</t>
+  </si>
+  <si>
+    <t>Duplicidade de VC com a 3450039648 ( digitada em sistema)</t>
+  </si>
+  <si>
+    <t> Chassi irregular,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAUER RASTERINHAS E ACESSORIOS LTDA ME       </t>
+  </si>
+  <si>
+    <t>Conforme regra de apólices canceladas houve quebra de vigência de
+70 dias, portanto deve-se reduzir duas classes de bônus, assim sen
+do o correto bônus  0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSE DE ARIMATEIA NUNES CAMBOIM              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identificamos uma divergência entre o modelo do
+veículo informado na transmissão da proposta. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">THAYRANNE MENEZES OLIVEIRA                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SONILDA DOS REIS FERREIRA                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MONICA FRANCA DE MENDONCA                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JORCELY ALVES SILVA COLUCCI                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANA LETICIA SLOMPO DE OLIVEIRA               </t>
+  </si>
+  <si>
+    <t>NUP Cancelamento 30.07.2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LEANDRO FERREIRA DA SILVA                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MATHEUS PENA LOPES                           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">WILDICEYA DE MENDONCA SANTANA                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANDREA ROMERO DE SOUZA                       </t>
+  </si>
+  <si>
+    <t>***FRUSTRADO**CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTO INCORRETA: Foto 45º - Frente e Lateral Direita (Não tirou foto do passo solicitado.). Foto 45º - Frente e Lateral Esquerda (Não tirou foto do passo solicitado.).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THIAGO SABINO DE SOUZA                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">IVAR MOTA COMPASSO                           </t>
+  </si>
+  <si>
+    <t>***FRUSTRADO**CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTO INCORRETA: Foto 45º - Frente e Lateral Direita (Cortando frente, Foto com placa obstruída). Foto 45º - Frente e Lateral Esquerda (Foto com placa obstruída).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DORIVAL MACHADO FILHO                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EVANDRO EUSTAQUIO MORAIS                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PATRICK ROCHA CAMARGO                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DAIANE PIRES DA SILVA                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FERNANDO MACHADO FERREIRA                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LETICIA MORAES DOS SANTOS                    </t>
   </si>
 </sst>
 </file>
@@ -487,7 +580,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -664,12 +757,71 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -769,7 +921,85 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" indent="5"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3273,7 +3503,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" ht="29.25">
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
@@ -3289,7 +3519,7 @@
       <c r="E2" s="21">
         <v>3450029440</v>
       </c>
-      <c r="F2" s="23" t="s">
+      <c r="F2" s="39" t="s">
         <v>85</v>
       </c>
       <c r="G2" s="6" t="s">
@@ -3959,7 +4189,7 @@
       <c r="G25" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="H25" s="39" t="s">
+      <c r="H25" s="9" t="s">
         <v>117</v>
       </c>
       <c r="I25" s="28">
@@ -3988,7 +4218,7 @@
       <c r="G26" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="H26" s="39" t="s">
+      <c r="H26" s="9" t="s">
         <v>119</v>
       </c>
       <c r="I26" s="28">
@@ -4017,7 +4247,7 @@
       <c r="G27" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="H27" s="39" t="s">
+      <c r="H27" s="9" t="s">
         <v>22</v>
       </c>
       <c r="I27" s="28">
@@ -4046,7 +4276,7 @@
       <c r="G28" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="H28" s="39" t="s">
+      <c r="H28" s="9" t="s">
         <v>22</v>
       </c>
       <c r="I28" s="28">
@@ -4344,20 +4574,20 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BD26F43-5C8A-4C67-93F6-3B4E17ED8491}">
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:BO55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="25.7109375" style="16" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.28515625" customWidth="1"/>
-    <col min="6" max="6" width="36" customWidth="1"/>
+    <col min="4" max="4" width="15.85546875" customWidth="1"/>
+    <col min="5" max="5" width="19" customWidth="1"/>
+    <col min="6" max="6" width="47.7109375" customWidth="1"/>
     <col min="7" max="7" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="53.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21" customWidth="1"/>
+    <col min="8" max="8" width="59.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21" style="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:67">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4386,295 +4616,712 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:67">
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="9"/>
-    </row>
-    <row r="3" spans="1:9">
+      <c r="B2" s="7">
+        <v>45867</v>
+      </c>
+      <c r="C2" s="7">
+        <v>45869</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="8">
+        <v>3450040121</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="3" spans="1:67">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="9"/>
-    </row>
-    <row r="4" spans="1:9">
+      <c r="B3" s="7">
+        <v>45867</v>
+      </c>
+      <c r="C3" s="7">
+        <v>45869</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="8">
+        <v>3450039406</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="4" spans="1:67">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="11"/>
-    </row>
-    <row r="5" spans="1:9">
+      <c r="B4" s="7">
+        <v>45868</v>
+      </c>
+      <c r="C4" s="7">
+        <v>45869</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="21">
+        <v>3450041309</v>
+      </c>
+      <c r="F4" s="52" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="I4" s="28"/>
+    </row>
+    <row r="5" spans="1:67">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="11"/>
-    </row>
-    <row r="6" spans="1:9">
+      <c r="B5" s="7">
+        <v>45856</v>
+      </c>
+      <c r="C5" s="7">
+        <v>45869</v>
+      </c>
+      <c r="D5" s="21">
+        <v>133496787</v>
+      </c>
+      <c r="E5" s="21">
+        <v>3450032542</v>
+      </c>
+      <c r="F5" s="52" t="s">
+        <v>127</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="I5" s="28">
+        <v>45861</v>
+      </c>
+    </row>
+    <row r="6" spans="1:67">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="11"/>
-    </row>
-    <row r="7" spans="1:9">
+      <c r="B6" s="7">
+        <v>45856</v>
+      </c>
+      <c r="C6" s="7">
+        <v>45869</v>
+      </c>
+      <c r="D6" s="58">
+        <v>133504944</v>
+      </c>
+      <c r="E6" s="44">
+        <v>3450032905</v>
+      </c>
+      <c r="F6" s="43" t="s">
+        <v>129</v>
+      </c>
+      <c r="G6" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="H6" s="23" t="s">
+        <v>130</v>
+      </c>
+      <c r="I6" s="28">
+        <v>45861</v>
+      </c>
+    </row>
+    <row r="7" spans="1:67">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="11"/>
-    </row>
-    <row r="8" spans="1:9">
+      <c r="B7" s="7">
+        <v>45857</v>
+      </c>
+      <c r="C7" s="7">
+        <v>45869</v>
+      </c>
+      <c r="D7" s="58">
+        <v>133520636</v>
+      </c>
+      <c r="E7" s="44">
+        <v>3450033664</v>
+      </c>
+      <c r="F7" s="43" t="s">
+        <v>131</v>
+      </c>
+      <c r="G7" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="H7" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="I7" s="28">
+        <v>45857</v>
+      </c>
+    </row>
+    <row r="8" spans="1:67">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="11"/>
-    </row>
-    <row r="9" spans="1:9">
+      <c r="B8" s="7">
+        <v>45861</v>
+      </c>
+      <c r="C8" s="7">
+        <v>45869</v>
+      </c>
+      <c r="D8" s="58">
+        <v>133587093</v>
+      </c>
+      <c r="E8" s="44">
+        <v>3450036381</v>
+      </c>
+      <c r="F8" s="43" t="s">
+        <v>132</v>
+      </c>
+      <c r="G8" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="I8" s="28">
+        <v>45861</v>
+      </c>
+    </row>
+    <row r="9" spans="1:67">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="11"/>
-    </row>
-    <row r="10" spans="1:9">
+      <c r="B9" s="7">
+        <v>45862</v>
+      </c>
+      <c r="C9" s="7">
+        <v>45869</v>
+      </c>
+      <c r="D9" s="58">
+        <v>133604806</v>
+      </c>
+      <c r="E9" s="44">
+        <v>3450037130</v>
+      </c>
+      <c r="F9" s="43" t="s">
+        <v>133</v>
+      </c>
+      <c r="G9" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="H9" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="I9" s="28">
+        <v>45862</v>
+      </c>
+    </row>
+    <row r="10" spans="1:67">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="11"/>
-    </row>
-    <row r="11" spans="1:9">
+      <c r="B10" s="7">
+        <v>45863</v>
+      </c>
+      <c r="C10" s="7">
+        <v>45869</v>
+      </c>
+      <c r="D10" s="58">
+        <v>133623704</v>
+      </c>
+      <c r="E10" s="44">
+        <v>3450037767</v>
+      </c>
+      <c r="F10" s="43" t="s">
+        <v>134</v>
+      </c>
+      <c r="G10" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="I10" s="28">
+        <v>45867</v>
+      </c>
+    </row>
+    <row r="11" spans="1:67">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="11"/>
-    </row>
-    <row r="12" spans="1:9">
+      <c r="B11" s="7">
+        <v>45867</v>
+      </c>
+      <c r="C11" s="7">
+        <v>45869</v>
+      </c>
+      <c r="D11" s="58">
+        <v>133660041</v>
+      </c>
+      <c r="E11" s="44">
+        <v>3450039307</v>
+      </c>
+      <c r="F11" s="43" t="s">
+        <v>135</v>
+      </c>
+      <c r="G11" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="I11" s="28">
+        <v>45868</v>
+      </c>
+    </row>
+    <row r="12" spans="1:67">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="11"/>
-    </row>
-    <row r="13" spans="1:9">
+      <c r="B12" s="7">
+        <v>45867</v>
+      </c>
+      <c r="C12" s="7">
+        <v>45869</v>
+      </c>
+      <c r="D12" s="58">
+        <v>133657083</v>
+      </c>
+      <c r="E12" s="44">
+        <v>3450039186</v>
+      </c>
+      <c r="F12" s="43" t="s">
+        <v>137</v>
+      </c>
+      <c r="G12" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="I12" s="28">
+        <v>45868</v>
+      </c>
+    </row>
+    <row r="13" spans="1:67">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="11"/>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="A14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="11"/>
-    </row>
-    <row r="15" spans="1:9">
-      <c r="A15" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="11"/>
-    </row>
-    <row r="16" spans="1:9">
-      <c r="A16" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="11"/>
+      <c r="B13" s="7">
+        <v>45868</v>
+      </c>
+      <c r="C13" s="7">
+        <v>45869</v>
+      </c>
+      <c r="D13" s="58">
+        <v>133678116</v>
+      </c>
+      <c r="E13" s="44">
+        <v>3450040451</v>
+      </c>
+      <c r="F13" s="43" t="s">
+        <v>138</v>
+      </c>
+      <c r="G13" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I13" s="28">
+        <v>45868</v>
+      </c>
+    </row>
+    <row r="14" spans="1:67">
+      <c r="A14" s="47" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="48">
+        <v>45860</v>
+      </c>
+      <c r="C14" s="7">
+        <v>45869</v>
+      </c>
+      <c r="D14" s="59">
+        <v>133568893</v>
+      </c>
+      <c r="E14" s="50">
+        <v>3450035590</v>
+      </c>
+      <c r="F14" s="49" t="s">
+        <v>139</v>
+      </c>
+      <c r="G14" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="H14" s="61" t="s">
+        <v>65</v>
+      </c>
+      <c r="I14" s="28">
+        <v>45868</v>
+      </c>
+    </row>
+    <row r="15" spans="1:67" s="45" customFormat="1">
+      <c r="A15" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="42">
+        <v>45862</v>
+      </c>
+      <c r="C15" s="40">
+        <v>45869</v>
+      </c>
+      <c r="D15" s="58">
+        <v>133591971</v>
+      </c>
+      <c r="E15" s="44">
+        <v>3450036580</v>
+      </c>
+      <c r="F15" s="43" t="s">
+        <v>140</v>
+      </c>
+      <c r="G15" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="H15" s="65" t="s">
+        <v>141</v>
+      </c>
+      <c r="I15" s="64">
+        <v>45862</v>
+      </c>
+      <c r="J15" s="25"/>
+      <c r="K15" s="25"/>
+      <c r="L15" s="25"/>
+      <c r="M15" s="25"/>
+      <c r="N15" s="25"/>
+      <c r="O15" s="25"/>
+      <c r="P15" s="25"/>
+      <c r="Q15" s="25"/>
+      <c r="R15" s="25"/>
+      <c r="S15" s="25"/>
+      <c r="T15" s="25"/>
+      <c r="U15" s="25"/>
+      <c r="V15" s="25"/>
+      <c r="W15" s="25"/>
+      <c r="X15" s="25"/>
+      <c r="Y15" s="25"/>
+      <c r="Z15" s="25"/>
+      <c r="AA15" s="25"/>
+      <c r="AB15" s="25"/>
+      <c r="AC15" s="25"/>
+      <c r="AD15" s="25"/>
+      <c r="AE15" s="25"/>
+      <c r="AF15" s="25"/>
+      <c r="AG15" s="25"/>
+      <c r="AH15" s="25"/>
+      <c r="AI15" s="25"/>
+      <c r="AJ15" s="25"/>
+      <c r="AK15" s="25"/>
+      <c r="AL15" s="25"/>
+      <c r="AM15" s="25"/>
+      <c r="AN15" s="25"/>
+      <c r="AO15" s="25"/>
+      <c r="AP15" s="25"/>
+      <c r="AQ15" s="25"/>
+      <c r="AR15" s="25"/>
+      <c r="AS15" s="25"/>
+      <c r="AT15" s="25"/>
+      <c r="AU15" s="25"/>
+      <c r="AV15" s="25"/>
+      <c r="AW15" s="25"/>
+      <c r="AX15" s="25"/>
+      <c r="AY15" s="25"/>
+      <c r="AZ15" s="25"/>
+      <c r="BA15" s="25"/>
+      <c r="BB15" s="25"/>
+      <c r="BC15" s="25"/>
+      <c r="BD15" s="25"/>
+      <c r="BE15" s="25"/>
+      <c r="BF15" s="25"/>
+      <c r="BG15" s="25"/>
+      <c r="BH15" s="25"/>
+      <c r="BI15" s="25"/>
+      <c r="BJ15" s="25"/>
+      <c r="BK15" s="25"/>
+      <c r="BL15" s="25"/>
+      <c r="BM15" s="25"/>
+      <c r="BN15" s="25"/>
+      <c r="BO15" s="63"/>
+    </row>
+    <row r="16" spans="1:67">
+      <c r="A16" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="54">
+        <v>45869</v>
+      </c>
+      <c r="C16" s="7">
+        <v>45869</v>
+      </c>
+      <c r="D16" s="60">
+        <v>133699787</v>
+      </c>
+      <c r="E16" s="56">
+        <v>3450041353</v>
+      </c>
+      <c r="F16" s="55" t="s">
+        <v>142</v>
+      </c>
+      <c r="G16" s="57" t="s">
+        <v>21</v>
+      </c>
+      <c r="H16" s="62" t="s">
+        <v>22</v>
+      </c>
+      <c r="I16" s="28">
+        <v>45869</v>
+      </c>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="11"/>
+      <c r="A17" s="66" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="7">
+        <v>45862</v>
+      </c>
+      <c r="C17" s="7">
+        <v>45869</v>
+      </c>
+      <c r="D17" s="24">
+        <v>133596080</v>
+      </c>
+      <c r="E17" s="18">
+        <v>3450036766</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="G17" s="67" t="s">
+        <v>24</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="I17" s="28">
+        <v>45862</v>
+      </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="11"/>
+      <c r="B18" s="7">
+        <v>45861</v>
+      </c>
+      <c r="C18" s="7">
+        <v>45869</v>
+      </c>
+      <c r="D18" s="58">
+        <v>133575328</v>
+      </c>
+      <c r="E18" s="44">
+        <v>3450035886</v>
+      </c>
+      <c r="F18" s="43" t="s">
+        <v>145</v>
+      </c>
+      <c r="G18" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I18" s="28">
+        <v>45861</v>
+      </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="11"/>
+      <c r="B19" s="7">
+        <v>45861</v>
+      </c>
+      <c r="C19" s="7">
+        <v>45869</v>
+      </c>
+      <c r="D19" s="58">
+        <v>133579818</v>
+      </c>
+      <c r="E19" s="44">
+        <v>3450036073</v>
+      </c>
+      <c r="F19" s="43" t="s">
+        <v>146</v>
+      </c>
+      <c r="G19" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I19" s="28">
+        <v>45861</v>
+      </c>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="6"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="9"/>
+      <c r="A20" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="7">
+        <v>45861</v>
+      </c>
+      <c r="C20" s="7">
+        <v>45869</v>
+      </c>
+      <c r="D20" s="58">
+        <v>133583157</v>
+      </c>
+      <c r="E20" s="44">
+        <v>3450036194</v>
+      </c>
+      <c r="F20" s="43" t="s">
+        <v>147</v>
+      </c>
+      <c r="G20" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I20" s="28">
+        <v>45861</v>
+      </c>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="6"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="9"/>
+      <c r="A21" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="7">
+        <v>45861</v>
+      </c>
+      <c r="C21" s="7">
+        <v>45869</v>
+      </c>
+      <c r="D21" s="58">
+        <v>133587403</v>
+      </c>
+      <c r="E21" s="44">
+        <v>3450036403</v>
+      </c>
+      <c r="F21" s="43" t="s">
+        <v>148</v>
+      </c>
+      <c r="G21" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I21" s="28">
+        <v>45861</v>
+      </c>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="6"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="9"/>
+      <c r="A22" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="7">
+        <v>45861</v>
+      </c>
+      <c r="C22" s="7">
+        <v>45869</v>
+      </c>
+      <c r="D22" s="58">
+        <v>133587604</v>
+      </c>
+      <c r="E22" s="44">
+        <v>3450036447</v>
+      </c>
+      <c r="F22" s="43" t="s">
+        <v>149</v>
+      </c>
+      <c r="G22" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I22" s="28">
+        <v>45861</v>
+      </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="6"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="9"/>
+      <c r="A23" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="7">
+        <v>45861</v>
+      </c>
+      <c r="C23" s="7">
+        <v>45869</v>
+      </c>
+      <c r="D23" s="58">
+        <v>133587995</v>
+      </c>
+      <c r="E23" s="44">
+        <v>3450036470</v>
+      </c>
+      <c r="F23" s="43" t="s">
+        <v>150</v>
+      </c>
+      <c r="G23" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I23" s="28">
+        <v>45861</v>
+      </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="6"/>
       <c r="B24" s="8"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="6"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="44"/>
+      <c r="E24" s="44"/>
+      <c r="F24" s="45"/>
+      <c r="G24" s="20"/>
       <c r="H24" s="9"/>
+      <c r="I24" s="28"/>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="6"/>
       <c r="B25" s="8"/>
       <c r="C25" s="7"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="9"/>
+      <c r="D25" s="22"/>
+      <c r="E25" s="22"/>
+      <c r="F25" s="15"/>
       <c r="G25" s="6"/>
       <c r="H25" s="9"/>
     </row>
@@ -4978,27 +5625,17 @@
       <c r="G55" s="6"/>
       <c r="H55" s="9"/>
     </row>
-    <row r="56" spans="1:8">
-      <c r="A56" s="6"/>
-      <c r="B56" s="8"/>
-      <c r="C56" s="7"/>
-      <c r="D56" s="8"/>
-      <c r="E56" s="8"/>
-      <c r="F56" s="9"/>
-      <c r="G56" s="6"/>
-      <c r="H56" s="9"/>
-    </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="1">
+    <cfRule type="notContainsBlanks" priority="4">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A19" xr:uid="{F535CD1B-7EC8-4CD4-9DE2-4943F25AAD12}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A23" xr:uid="{F535CD1B-7EC8-4CD4-9DE2-4943F25AAD12}">
       <formula1>$J$2</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G42" xr:uid="{9AF2051F-77D3-4586-8B0A-6A9380E3F6D6}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G41" xr:uid="{9AF2051F-77D3-4586-8B0A-6A9380E3F6D6}">
       <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7528,7 +8165,7 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5341E62A-60AC-4ABD-ABD0-CD6F81787338}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0E37909-9E11-4B8E-93BE-E6513333F97F}"/>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>

--- a/Data Files/Backoffce/IndexacaoFG/Arquivos/Relatório de Recusas  28.07.2025 a 03.08.2025.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/Arquivos/Relatório de Recusas  28.07.2025 a 03.08.2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms.sharepoint.com/teams/BR0010-4356589/Shared Documents/BACK-OFFICE SME/Santander/2025/Relatório de Recusas/05. Maio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E7B21216-FB5A-46BA-9299-A988CD759C92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7E1C0490-F79D-4981-851B-B5F5A068B3A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="28.07" sheetId="8" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="172">
   <si>
     <t>SEGURADORA</t>
   </si>
@@ -520,6 +520,69 @@
   </si>
   <si>
     <t xml:space="preserve">LETICIA MORAES DOS SANTOS                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TATIANA PAIVA MARTINS                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DROGARIA DROGAMED SELVIRIA LTDA ME           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EDUARDO BARBOSA WATACABE                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">E E CONSTRUCOES E ACABAMENTOS LTDA ME        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">UBIRAJARA FIRPO                              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">NICOLAS JUNIO OLIVEIRA DA SILVA              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">A K NET TELECOM LTDA ME                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DAYANE PADILHA                               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSIAS PEREIRA                               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SERGIO SONEGO                                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JAIRO TELES NOBRE                            </t>
+  </si>
+  <si>
+    <t>Santander - Bônus correto deve ser {}, favor corrigir.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EVANIR FREITAS CAVALCANTE                    </t>
+  </si>
+  <si>
+    <t>falta de vistoria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSE ROBERTO DE ALMEIDA SACRAMENTO           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SONIA REGINA NUNES LEMOS SCHMIDT             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANDRA CRISTINA DA SILVA                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAFAEL MARQUES BARROSO                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">OZEIAS DOS SANTOS ARTEFATOS DE CIMENTO ME    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALERIA GOMES DE ARAUJO                      </t>
+  </si>
+  <si>
+    <t>Santander - Veículo em duplicidade com proposta</t>
   </si>
 </sst>
 </file>
@@ -821,7 +884,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1000,12 +1063,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal_Plan2_1" xfId="1" xr:uid="{69F13A52-20D9-46CA-8619-BC7A1BA09FD8}"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="6">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2608,13 +2682,13 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2">
-    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3:E4">
-    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E5">
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
   </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A34" xr:uid="{05596F41-D45D-4DF0-82AF-FA8AAC9891B7}">
@@ -5649,13 +5723,13 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.140625" customWidth="1"/>
     <col min="3" max="3" width="18.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="26" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="31.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19" customWidth="1"/>
+    <col min="6" max="6" width="43.5703125" customWidth="1"/>
     <col min="7" max="7" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="36.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="18.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5692,147 +5766,305 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="9"/>
+      <c r="B2" s="7">
+        <v>45862</v>
+      </c>
+      <c r="C2" s="19">
+        <v>45870</v>
+      </c>
+      <c r="D2" s="24">
+        <v>133602703</v>
+      </c>
+      <c r="E2" s="18">
+        <v>3450037041</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="G2" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I2" s="28">
+        <v>45862</v>
+      </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="9"/>
+      <c r="B3" s="7">
+        <v>45862</v>
+      </c>
+      <c r="C3" s="19">
+        <v>45870</v>
+      </c>
+      <c r="D3" s="24">
+        <v>133596540</v>
+      </c>
+      <c r="E3" s="18">
+        <v>3450036799</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="G3" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I3" s="28">
+        <v>45862</v>
+      </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="11"/>
+      <c r="B4" s="7">
+        <v>45863</v>
+      </c>
+      <c r="C4" s="19">
+        <v>45870</v>
+      </c>
+      <c r="D4" s="24">
+        <v>133616571</v>
+      </c>
+      <c r="E4" s="18">
+        <v>3450037558</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="G4" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="I4" s="28">
+        <v>45867</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="11"/>
+      <c r="B5" s="7">
+        <v>45867</v>
+      </c>
+      <c r="C5" s="19">
+        <v>45870</v>
+      </c>
+      <c r="D5" s="24">
+        <v>133670979</v>
+      </c>
+      <c r="E5" s="18">
+        <v>3450040132</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="G5" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" s="28">
+        <v>45867</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="11"/>
+      <c r="B6" s="7">
+        <v>45862</v>
+      </c>
+      <c r="C6" s="19">
+        <v>45870</v>
+      </c>
+      <c r="D6" s="24">
+        <v>133593154</v>
+      </c>
+      <c r="E6" s="18">
+        <v>3450036612</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="G6" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I6" s="28">
+        <v>45862</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="11"/>
+      <c r="B7" s="7">
+        <v>45862</v>
+      </c>
+      <c r="C7" s="19">
+        <v>45870</v>
+      </c>
+      <c r="D7" s="24">
+        <v>133597679</v>
+      </c>
+      <c r="E7" s="18">
+        <v>3450036843</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="G7" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="I7" s="28">
+        <v>45862</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="11"/>
+      <c r="B8" s="7">
+        <v>45862</v>
+      </c>
+      <c r="C8" s="19">
+        <v>45870</v>
+      </c>
+      <c r="D8" s="24">
+        <v>133598451</v>
+      </c>
+      <c r="E8" s="18">
+        <v>3450036898</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="G8" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="I8" s="28">
+        <v>45862</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="11"/>
+      <c r="B9" s="7">
+        <v>45862</v>
+      </c>
+      <c r="C9" s="19">
+        <v>45870</v>
+      </c>
+      <c r="D9" s="24">
+        <v>133601002</v>
+      </c>
+      <c r="E9" s="18">
+        <v>3450036986</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="G9" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I9" s="28">
+        <v>45862</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="11"/>
+      <c r="B10" s="7">
+        <v>45862</v>
+      </c>
+      <c r="C10" s="19">
+        <v>45870</v>
+      </c>
+      <c r="D10" s="24">
+        <v>133608059</v>
+      </c>
+      <c r="E10" s="18">
+        <v>3450037283</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="G10" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I10" s="28">
+        <v>45862</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="11"/>
+      <c r="B11" s="7">
+        <v>45862</v>
+      </c>
+      <c r="C11" s="19">
+        <v>45870</v>
+      </c>
+      <c r="D11" s="24">
+        <v>133609410</v>
+      </c>
+      <c r="E11" s="18">
+        <v>3450037360</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="G11" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I11" s="28">
+        <v>45862</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="A12" s="6"/>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="12"/>
+      <c r="D12" s="22"/>
+      <c r="E12" s="30"/>
+      <c r="F12" s="31"/>
       <c r="G12" s="6"/>
       <c r="H12" s="9"/>
-      <c r="I12" s="11"/>
+      <c r="I12" s="28"/>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="A13" s="6"/>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
       <c r="D13" s="8"/>
@@ -5840,12 +6072,10 @@
       <c r="F13" s="12"/>
       <c r="G13" s="6"/>
       <c r="H13" s="9"/>
-      <c r="I13" s="11"/>
+      <c r="I13" s="28"/>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="A14" s="6"/>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
       <c r="D14" s="8"/>
@@ -5853,12 +6083,10 @@
       <c r="F14" s="12"/>
       <c r="G14" s="6"/>
       <c r="H14" s="9"/>
-      <c r="I14" s="11"/>
+      <c r="I14" s="28"/>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="A15" s="6"/>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
       <c r="D15" s="8"/>
@@ -5866,12 +6094,10 @@
       <c r="F15" s="12"/>
       <c r="G15" s="6"/>
       <c r="H15" s="9"/>
-      <c r="I15" s="11"/>
+      <c r="I15" s="28"/>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="A16" s="6"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
       <c r="D16" s="8"/>
@@ -5879,12 +6105,10 @@
       <c r="F16" s="12"/>
       <c r="G16" s="6"/>
       <c r="H16" s="9"/>
-      <c r="I16" s="11"/>
+      <c r="I16" s="28"/>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="A17" s="6"/>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
       <c r="D17" s="8"/>
@@ -5895,9 +6119,7 @@
       <c r="I17" s="11"/>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="A18" s="6"/>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
       <c r="D18" s="8"/>
@@ -5908,9 +6130,7 @@
       <c r="I18" s="11"/>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="A19" s="6"/>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
       <c r="D19" s="8"/>
@@ -6292,7 +6512,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="1">
+    <cfRule type="notContainsBlanks" priority="2">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6310,15 +6530,15 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43D38813-FAE5-45C6-9D51-7607EDAA916D}">
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" customWidth="1"/>
     <col min="3" max="3" width="18.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.5703125" customWidth="1"/>
     <col min="5" max="5" width="24.28515625" customWidth="1"/>
-    <col min="6" max="6" width="36" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="36.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="20.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="42" customWidth="1"/>
     <col min="9" max="9" width="18.7109375" style="16" bestFit="1" customWidth="1"/>
@@ -6357,123 +6577,247 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="9"/>
-      <c r="I2"/>
+      <c r="B2" s="7">
+        <v>45860</v>
+      </c>
+      <c r="C2" s="19">
+        <v>45871</v>
+      </c>
+      <c r="D2" s="24">
+        <v>133561487</v>
+      </c>
+      <c r="E2" s="18">
+        <v>3450035336</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="G2" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="H2" s="68" t="s">
+        <v>162</v>
+      </c>
+      <c r="I2" s="28">
+        <v>45860</v>
+      </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="9"/>
-      <c r="I3"/>
+      <c r="B3" s="7">
+        <v>45856</v>
+      </c>
+      <c r="C3" s="19">
+        <v>45871</v>
+      </c>
+      <c r="D3" s="24">
+        <v>133525002</v>
+      </c>
+      <c r="E3" s="18">
+        <v>3450033092</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="G3" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="I3" s="28">
+        <v>45856</v>
+      </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="11"/>
+      <c r="B4" s="7">
+        <v>45859</v>
+      </c>
+      <c r="C4" s="19">
+        <v>45871</v>
+      </c>
+      <c r="D4" s="24">
+        <v>133525705</v>
+      </c>
+      <c r="E4" s="18">
+        <v>3450033752</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="G4" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="I4" s="28">
+        <v>45859</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="11"/>
+      <c r="B5" s="7">
+        <v>45859</v>
+      </c>
+      <c r="C5" s="19">
+        <v>45871</v>
+      </c>
+      <c r="D5" s="24">
+        <v>133527815</v>
+      </c>
+      <c r="E5" s="18">
+        <v>3450033829</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="G5" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="I5" s="28">
+        <v>45859</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="11"/>
+      <c r="B6" s="7">
+        <v>45859</v>
+      </c>
+      <c r="C6" s="19">
+        <v>45871</v>
+      </c>
+      <c r="D6" s="24">
+        <v>133535336</v>
+      </c>
+      <c r="E6" s="18">
+        <v>3450034148</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="G6" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="I6" s="28">
+        <v>45859</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="11"/>
+      <c r="B7" s="7">
+        <v>45859</v>
+      </c>
+      <c r="C7" s="19">
+        <v>45871</v>
+      </c>
+      <c r="D7" s="24">
+        <v>133537615</v>
+      </c>
+      <c r="E7" s="18">
+        <v>3450034270</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="G7" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="I7" s="28">
+        <v>45859</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="11"/>
-    </row>
-    <row r="9" spans="1:9">
+      <c r="B8" s="7">
+        <v>45859</v>
+      </c>
+      <c r="C8" s="19">
+        <v>45871</v>
+      </c>
+      <c r="D8" s="24">
+        <v>133541882</v>
+      </c>
+      <c r="E8" s="18">
+        <v>3450034456</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="G8" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="I8" s="28">
+        <v>45859</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="29.25">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="11"/>
+      <c r="B9" s="7">
+        <v>45860</v>
+      </c>
+      <c r="C9" s="19">
+        <v>45871</v>
+      </c>
+      <c r="D9" s="24">
+        <v>133554784</v>
+      </c>
+      <c r="E9" s="18">
+        <v>3450034962</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="G9" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="H9" s="32" t="s">
+        <v>171</v>
+      </c>
+      <c r="I9" s="28">
+        <v>45860</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="A10" s="6"/>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="12"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="30"/>
+      <c r="F10" s="31"/>
       <c r="G10" s="6"/>
       <c r="H10" s="9"/>
-      <c r="I10" s="11"/>
+      <c r="I10" s="28"/>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="A11" s="6"/>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
       <c r="D11" s="8"/>
@@ -6481,119 +6825,103 @@
       <c r="F11" s="12"/>
       <c r="G11" s="6"/>
       <c r="H11" s="9"/>
-      <c r="I11" s="11"/>
+      <c r="I11" s="28"/>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" s="7"/>
+      <c r="A12" s="6"/>
+      <c r="B12" s="8"/>
       <c r="C12" s="7"/>
       <c r="D12" s="8"/>
       <c r="E12" s="14"/>
-      <c r="F12" s="12"/>
+      <c r="F12" s="13"/>
       <c r="G12" s="6"/>
       <c r="H12" s="9"/>
-      <c r="I12" s="11"/>
+      <c r="I12" s="28"/>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" s="7"/>
+      <c r="A13" s="6"/>
+      <c r="B13" s="8"/>
       <c r="C13" s="7"/>
       <c r="D13" s="8"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="12"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="15"/>
       <c r="G13" s="6"/>
       <c r="H13" s="9"/>
-      <c r="I13" s="11"/>
+      <c r="I13" s="28"/>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B14" s="7"/>
+      <c r="A14" s="6"/>
+      <c r="B14" s="8"/>
       <c r="C14" s="7"/>
       <c r="D14" s="8"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="12"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="9"/>
       <c r="G14" s="6"/>
       <c r="H14" s="9"/>
-      <c r="I14" s="11"/>
+      <c r="I14" s="28"/>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B15" s="7"/>
+      <c r="A15" s="6"/>
+      <c r="B15" s="8"/>
       <c r="C15" s="7"/>
       <c r="D15" s="8"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="12"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="9"/>
       <c r="G15" s="6"/>
       <c r="H15" s="9"/>
-      <c r="I15" s="11"/>
+      <c r="I15" s="28"/>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B16" s="7"/>
+      <c r="A16" s="6"/>
+      <c r="B16" s="8"/>
       <c r="C16" s="7"/>
       <c r="D16" s="8"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="12"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="9"/>
       <c r="G16" s="6"/>
       <c r="H16" s="9"/>
-      <c r="I16" s="11"/>
+      <c r="I16"/>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B17" s="7"/>
+      <c r="A17" s="6"/>
+      <c r="B17" s="8"/>
       <c r="C17" s="7"/>
       <c r="D17" s="8"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="12"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="9"/>
       <c r="G17" s="6"/>
       <c r="H17" s="9"/>
-      <c r="I17" s="11"/>
+      <c r="I17"/>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B18" s="7"/>
+      <c r="A18" s="6"/>
+      <c r="B18" s="8"/>
       <c r="C18" s="7"/>
       <c r="D18" s="8"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="12"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="9"/>
       <c r="G18" s="6"/>
       <c r="H18" s="9"/>
-      <c r="I18" s="11"/>
+      <c r="I18"/>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B19" s="7"/>
+      <c r="A19" s="6"/>
+      <c r="B19" s="8"/>
       <c r="C19" s="7"/>
       <c r="D19" s="8"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="12"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="9"/>
       <c r="G19" s="6"/>
       <c r="H19" s="9"/>
-      <c r="I19" s="11"/>
+      <c r="I19"/>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="6"/>
       <c r="B20" s="8"/>
       <c r="C20" s="7"/>
       <c r="D20" s="8"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="13"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="9"/>
       <c r="G20" s="6"/>
       <c r="H20" s="9"/>
       <c r="I20"/>
@@ -6604,7 +6932,7 @@
       <c r="C21" s="7"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
-      <c r="F21" s="15"/>
+      <c r="F21" s="9"/>
       <c r="G21" s="6"/>
       <c r="H21" s="9"/>
       <c r="I21"/>
@@ -6906,105 +7234,20 @@
       <c r="H48" s="9"/>
       <c r="I48"/>
     </row>
-    <row r="49" spans="1:9">
-      <c r="A49" s="6"/>
-      <c r="B49" s="8"/>
-      <c r="C49" s="7"/>
-      <c r="D49" s="8"/>
-      <c r="E49" s="8"/>
-      <c r="F49" s="9"/>
-      <c r="G49" s="6"/>
-      <c r="H49" s="9"/>
-      <c r="I49"/>
-    </row>
-    <row r="50" spans="1:9">
-      <c r="A50" s="6"/>
-      <c r="B50" s="8"/>
-      <c r="C50" s="7"/>
-      <c r="D50" s="8"/>
-      <c r="E50" s="8"/>
-      <c r="F50" s="9"/>
-      <c r="G50" s="6"/>
-      <c r="H50" s="9"/>
-      <c r="I50"/>
-    </row>
-    <row r="51" spans="1:9">
-      <c r="A51" s="6"/>
-      <c r="B51" s="8"/>
-      <c r="C51" s="7"/>
-      <c r="D51" s="8"/>
-      <c r="E51" s="8"/>
-      <c r="F51" s="9"/>
-      <c r="G51" s="6"/>
-      <c r="H51" s="9"/>
-      <c r="I51"/>
-    </row>
-    <row r="52" spans="1:9">
-      <c r="A52" s="6"/>
-      <c r="B52" s="8"/>
-      <c r="C52" s="7"/>
-      <c r="D52" s="8"/>
-      <c r="E52" s="8"/>
-      <c r="F52" s="9"/>
-      <c r="G52" s="6"/>
-      <c r="H52" s="9"/>
-      <c r="I52"/>
-    </row>
-    <row r="53" spans="1:9">
-      <c r="A53" s="6"/>
-      <c r="B53" s="8"/>
-      <c r="C53" s="7"/>
-      <c r="D53" s="8"/>
-      <c r="E53" s="8"/>
-      <c r="F53" s="9"/>
-      <c r="G53" s="6"/>
-      <c r="H53" s="9"/>
-      <c r="I53"/>
-    </row>
-    <row r="54" spans="1:9">
-      <c r="A54" s="6"/>
-      <c r="B54" s="8"/>
-      <c r="C54" s="7"/>
-      <c r="D54" s="8"/>
-      <c r="E54" s="8"/>
-      <c r="F54" s="9"/>
-      <c r="G54" s="6"/>
-      <c r="H54" s="9"/>
-      <c r="I54"/>
-    </row>
-    <row r="55" spans="1:9">
-      <c r="A55" s="6"/>
-      <c r="B55" s="8"/>
-      <c r="C55" s="7"/>
-      <c r="D55" s="8"/>
-      <c r="E55" s="8"/>
-      <c r="F55" s="9"/>
-      <c r="G55" s="6"/>
-      <c r="H55" s="9"/>
-      <c r="I55"/>
-    </row>
-    <row r="56" spans="1:9">
-      <c r="A56" s="6"/>
-      <c r="B56" s="8"/>
-      <c r="C56" s="7"/>
-      <c r="D56" s="8"/>
-      <c r="E56" s="8"/>
-      <c r="F56" s="9"/>
-      <c r="G56" s="6"/>
-      <c r="H56" s="9"/>
-      <c r="I56"/>
-    </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="1">
+    <cfRule type="notContainsBlanks" priority="2">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F9 D2:D9">
+    <cfRule type="duplicateValues" dxfId="2" priority="14"/>
+  </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A19" xr:uid="{33F609D2-9B9D-4D52-B406-6DFCF1363D87}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A11" xr:uid="{33F609D2-9B9D-4D52-B406-6DFCF1363D87}">
       <formula1>$J$2</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G42" xr:uid="{1B2A036A-428B-43C6-B539-9B85A74E7043}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G34" xr:uid="{1B2A036A-428B-43C6-B539-9B85A74E7043}">
       <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7692,46 +7935,53 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-477958</_dlc_DocId>
-    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-477958</Url>
-      <Description>QAFFA7D2F2TC-2102087286-477958</Description>
-    </_dlc_DocIdUrl>
-    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </DossierOwner>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ccca9d190a3c43e89f73773ee806c8b5>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ia4b831ccad64069ad2e0cbd870e9b8a>
-    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </alteradopor>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8107,53 +8357,46 @@
 </file>
 
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-477958</_dlc_DocId>
+    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-477958</Url>
+      <Description>QAFFA7D2F2TC-2102087286-477958</Description>
+    </_dlc_DocIdUrl>
+    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </DossierOwner>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ccca9d190a3c43e89f73773ee806c8b5>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ia4b831ccad64069ad2e0cbd870e9b8a>
+    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </alteradopor>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8161,7 +8404,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8169,5 +8412,5 @@
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
 </file>